--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2304 (group_metrics.csv)</t>
+          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2262 (group_metrics.csv)</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
         <v>124</v>
@@ -1084,13 +1084,13 @@
         <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3629032258064516</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1932773109243698</v>
+        <v>0.1843924972004479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5241492368569812</v>
       </c>
     </row>
     <row r="5">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
         <v>124</v>
@@ -1109,13 +1109,13 @@
         <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4435483870967742</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2934688905547227</v>
+        <v>0.2814814814814815</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5985414310681608</v>
+        <v>0.5947779938421649</v>
       </c>
     </row>
     <row r="6">
@@ -1140,7 +1140,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5068493150684932</v>
+        <v>0.5109571373689697</v>
       </c>
     </row>
     <row r="9">
@@ -1202,10 +1202,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1713027900396292</v>
+        <v>0.1712728367906377</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6220743511168214</v>
+        <v>0.6211888921974211</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2458911907820019</v>
+        <v>0.2866219126896772</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7655598561891277</v>
+        <v>0.7648114725882532</v>
       </c>
     </row>
     <row r="14">
@@ -1243,10 +1243,10 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02318305814993844</v>
+        <v>0.0225796197425291</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05971892607314804</v>
+        <v>0.0591389851267043</v>
       </c>
     </row>
     <row r="15">
@@ -1262,10 +1262,10 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004893096662891379</v>
+        <v>0.004949565365879021</v>
       </c>
       <c r="E15" t="n">
-        <v>0.009488478429132587</v>
+        <v>0.00960141583510787</v>
       </c>
     </row>
   </sheetData>
@@ -2235,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2286,7 +2286,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2304 (group_metrics.csv)</t>
+          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2262 (group_metrics.csv)</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
         <v>4100</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9996</v>
+        <v>24.9995</v>
       </c>
       <c r="F6" t="n">
         <v>4.1</v>
@@ -2410,7 +2410,7 @@
         <v>13000</v>
       </c>
       <c r="E7" t="n">
-        <v>23.5099</v>
+        <v>23.509</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
@@ -2440,7 +2440,7 @@
         <v>28200</v>
       </c>
       <c r="E8" t="n">
-        <v>22.9777</v>
+        <v>22.9751</v>
       </c>
       <c r="F8" t="n">
         <v>28.2</v>
@@ -2470,7 +2470,7 @@
         <v>50000</v>
       </c>
       <c r="E9" t="n">
-        <v>24.5349</v>
+        <v>24.4496</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
@@ -2530,7 +2530,7 @@
         <v>5500</v>
       </c>
       <c r="E11" t="n">
-        <v>33.844</v>
+        <v>33.8399</v>
       </c>
       <c r="F11" t="n">
         <v>5.5</v>
@@ -2590,7 +2590,7 @@
         <v>14000</v>
       </c>
       <c r="E13" t="n">
-        <v>19.9401</v>
+        <v>19.9395</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
@@ -2620,7 +2620,7 @@
         <v>5370</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7525</v>
+        <v>24.7523</v>
       </c>
       <c r="F14" t="n">
         <v>5.37</v>
@@ -2650,7 +2650,7 @@
         <v>15000</v>
       </c>
       <c r="E15" t="n">
-        <v>23.3788</v>
+        <v>23.3775</v>
       </c>
       <c r="F15" t="n">
         <v>15</v>
@@ -2680,7 +2680,7 @@
         <v>30500</v>
       </c>
       <c r="E16" t="n">
-        <v>22.8115</v>
+        <v>22.8086</v>
       </c>
       <c r="F16" t="n">
         <v>30.5</v>
@@ -2800,7 +2800,7 @@
         <v>4000</v>
       </c>
       <c r="E20" t="n">
-        <v>43.2062</v>
+        <v>43.202</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -2810,36 +2810,6 @@
       </c>
       <c r="H20" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fe/BaTiO2.4H0.6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fe</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>14000</v>
-      </c>
-      <c r="E21" t="n">
-        <v>19.9401</v>
-      </c>
-      <c r="F21" t="n">
-        <v>14</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="n">
         <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3975903614457831</v>
+        <v>0.6585365853658537</v>
       </c>
     </row>
     <row r="5">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="n">
         <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3734939759036144</v>
+        <v>0.6463414634146342</v>
       </c>
     </row>
     <row r="6">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
         <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1927710843373494</v>
+        <v>0.6951219512195121</v>
       </c>
     </row>
     <row r="7">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="n">
         <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.3902439024390244</v>
       </c>
     </row>
     <row r="10">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5542168674698795</v>
+        <v>0.6707317073170732</v>
       </c>
     </row>
     <row r="17">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.5148442756897049</v>
       </c>
     </row>
     <row r="22">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.550561797752809</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1413,7 @@
         <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>907.429</v>
+        <v>996.8064341210001</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1223.3</v>
+        <v>1765.1390014</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>896.438</v>
+        <v>982.367484386</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.65</v>
       </c>
       <c r="H8" t="n">
-        <v>1436.48</v>
+        <v>2169.77018622</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0.55</v>
       </c>
       <c r="H9" t="n">
-        <v>891.802</v>
+        <v>921.462422136</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>916.664</v>
+        <v>982.993781833</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0.28</v>
       </c>
       <c r="H11" t="n">
-        <v>2083.17</v>
+        <v>4160.08196374</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>0.15</v>
       </c>
       <c r="H12" t="n">
-        <v>1234.68</v>
+        <v>1862.68974212</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1062.21</v>
+        <v>1087.96098858</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0.0519</v>
       </c>
       <c r="H5" t="n">
-        <v>1170.17</v>
+        <v>2880.80431525</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1891,7 +1891,7 @@
         <v>0.0435</v>
       </c>
       <c r="H6" t="n">
-        <v>1081.53</v>
+        <v>2004.28418976</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0.0337</v>
       </c>
       <c r="H7" t="n">
-        <v>1363.01</v>
+        <v>4646.98361625</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0.0222</v>
       </c>
       <c r="H8" t="n">
-        <v>1067.49</v>
+        <v>2009.18035731</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0.0201</v>
       </c>
       <c r="H9" t="n">
-        <v>1100.63</v>
+        <v>1957.4814752</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0.0195</v>
       </c>
       <c r="H10" t="n">
-        <v>1882.45</v>
+        <v>2031.09272018</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0.0063</v>
       </c>
       <c r="H11" t="n">
-        <v>1054.68</v>
+        <v>8932.80492076</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>0.0055</v>
       </c>
       <c r="H12" t="n">
-        <v>1002.05</v>
+        <v>1118.48929052</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0.0046</v>
       </c>
       <c r="H13" t="n">
-        <v>1183.22</v>
+        <v>65521.3600459</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0.0044</v>
       </c>
       <c r="H14" t="n">
-        <v>1035.49</v>
+        <v>1297.31057863</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>1489.72</v>
+        <v>56428.4539703</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="n">
         <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.3975903614457831</v>
       </c>
     </row>
     <row r="5">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="n">
         <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6463414634146342</v>
+        <v>0.3734939759036144</v>
       </c>
     </row>
     <row r="6">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="n">
         <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6951219512195121</v>
+        <v>0.1927710843373494</v>
       </c>
     </row>
     <row r="7">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
         <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.7590361445783133</v>
       </c>
     </row>
     <row r="10">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6707317073170732</v>
+        <v>0.5542168674698795</v>
       </c>
     </row>
     <row r="17">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5148442756897049</v>
+        <v>0.2368421052631579</v>
       </c>
     </row>
     <row r="22">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8</v>
+        <v>0.550561797752809</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1413,7 @@
         <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>996.8064341210001</v>
+        <v>907.429</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1765.1390014</v>
+        <v>1223.3</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>982.367484386</v>
+        <v>896.438</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.65</v>
       </c>
       <c r="H8" t="n">
-        <v>2169.77018622</v>
+        <v>1436.48</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0.55</v>
       </c>
       <c r="H9" t="n">
-        <v>921.462422136</v>
+        <v>891.802</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>982.993781833</v>
+        <v>916.664</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0.28</v>
       </c>
       <c r="H11" t="n">
-        <v>4160.08196374</v>
+        <v>2083.17</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>0.15</v>
       </c>
       <c r="H12" t="n">
-        <v>1862.68974212</v>
+        <v>1234.68</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1087.96098858</v>
+        <v>1062.21</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0.0519</v>
       </c>
       <c r="H5" t="n">
-        <v>2880.80431525</v>
+        <v>1170.17</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1891,7 +1891,7 @@
         <v>0.0435</v>
       </c>
       <c r="H6" t="n">
-        <v>2004.28418976</v>
+        <v>1081.53</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0.0337</v>
       </c>
       <c r="H7" t="n">
-        <v>4646.98361625</v>
+        <v>1363.01</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0.0222</v>
       </c>
       <c r="H8" t="n">
-        <v>2009.18035731</v>
+        <v>1067.49</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0.0201</v>
       </c>
       <c r="H9" t="n">
-        <v>1957.4814752</v>
+        <v>1100.63</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0.0195</v>
       </c>
       <c r="H10" t="n">
-        <v>2031.09272018</v>
+        <v>1882.45</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0.0063</v>
       </c>
       <c r="H11" t="n">
-        <v>8932.80492076</v>
+        <v>1054.68</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>0.0055</v>
       </c>
       <c r="H12" t="n">
-        <v>1118.48929052</v>
+        <v>1002.05</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0.0046</v>
       </c>
       <c r="H13" t="n">
-        <v>65521.3600459</v>
+        <v>1183.22</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0.0044</v>
       </c>
       <c r="H14" t="n">
-        <v>1297.31057863</v>
+        <v>1035.49</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>56428.4539703</v>
+        <v>1489.72</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="5">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6463414634146342</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="6">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6951219512195121</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="10">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6707317073170732</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="17">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5148442756897049</v>
+        <v>0.1515151515151515</v>
       </c>
     </row>
     <row r="22">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1413,7 @@
         <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>996.8064341210001</v>
+        <v>907.428981751</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1765.1390014</v>
+        <v>1242.25295316</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>982.367484386</v>
+        <v>896.438398589</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.65</v>
       </c>
       <c r="H8" t="n">
-        <v>2169.77018622</v>
+        <v>1459.37183387</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0.55</v>
       </c>
       <c r="H9" t="n">
-        <v>921.462422136</v>
+        <v>891.802198348</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>982.993781833</v>
+        <v>916.663627744</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0.28</v>
       </c>
       <c r="H11" t="n">
-        <v>4160.08196374</v>
+        <v>2096.69366857</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>0.15</v>
       </c>
       <c r="H12" t="n">
-        <v>1862.68974212</v>
+        <v>1234.68078338</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1087.96098858</v>
+        <v>1062.20897971</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0.0519</v>
       </c>
       <c r="H5" t="n">
-        <v>2880.80431525</v>
+        <v>1170.17134434</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1891,7 +1891,7 @@
         <v>0.0435</v>
       </c>
       <c r="H6" t="n">
-        <v>2004.28418976</v>
+        <v>1081.52892928</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0.0337</v>
       </c>
       <c r="H7" t="n">
-        <v>4646.98361625</v>
+        <v>1363.00923765</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0.0222</v>
       </c>
       <c r="H8" t="n">
-        <v>2009.18035731</v>
+        <v>1067.49027074</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0.0201</v>
       </c>
       <c r="H9" t="n">
-        <v>1957.4814752</v>
+        <v>1104.6727405</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0.0195</v>
       </c>
       <c r="H10" t="n">
-        <v>2031.09272018</v>
+        <v>1882.44652844</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0.0063</v>
       </c>
       <c r="H11" t="n">
-        <v>8932.80492076</v>
+        <v>1054.67603102</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>0.0055</v>
       </c>
       <c r="H12" t="n">
-        <v>1118.48929052</v>
+        <v>1002.0514943</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0.0046</v>
       </c>
       <c r="H13" t="n">
-        <v>65521.3600459</v>
+        <v>1183.21956718</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0.0044</v>
       </c>
       <c r="H14" t="n">
-        <v>1297.31057863</v>
+        <v>1035.48720019</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>56428.4539703</v>
+        <v>1489.71735261</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,15 +494,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>leader changes by paper leaderboard (recycled CO)</t>
+          <t>leader changes by paper leaderboard: inert-limited loop (primary) and STY without the limit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (primary, variants.leaderboard_*)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv (cost_column) scored with meoh_candidates.aggregate; CI95: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json (STY) and analysis/meoh_main_result_stats_2026_10_06/summary.json (STY_no_limit), cluster_bootstrap.fraction_ci95</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bar height = fraction; hatched height = regret_gt5pct / groups</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -512,12 +516,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marker: STY leaderboard with inert CO</t>
+          <t>STY disagreements by kind, inert-limited loop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.inert_opt)</t>
+          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.inlet_limit_6.86pct.kinds)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -525,17 +529,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>error bar on STY: paper-cluster bootstrap</t>
+          <t>ammonia leader changes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/summary.json (cluster_bootstrap)</t>
+          <t>analysis/nh3_field_2026_10_06/summary.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -548,12 +552,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ammonia leader changes</t>
+          <t>what the mismatched comparisons differ by (primary)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/summary.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers)</t>
+          <t>analysis/nh3_field_2026_10_06/summary.json (primary.mismatch_kinds); plant-winner metal from group_metrics.csv + candidates.csv</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -561,30 +565,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>what the mismatched comparisons differ by (primary)</t>
+          <t>comparison group 10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/summary.json (primary.mismatch_kinds); plant-winner metal from group_metrics.csv + candidates.csv</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCH4; leaders of the inert-limited loop</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comparison group 10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+          <t>comparison group 10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -594,49 +602,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>x = STY (g_MeOH g_cat-1 h-1), y = cost_recycled_opt (EUR/t), marker area ~ SCH4</t>
+          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCO; leaders of the inert-limited loop</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comparison group 10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>comparison group 10.1002/aenm.201801772 | 400 C | 5 MPa | H2/N2 3 | 6.6e+04 mL/g/h</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv</t>
+          <t>analysis/nh3_field_2026_10_06/candidates.csv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>x = STY (g_MeOH g_cat-1 h-1), y = cost_recycled_opt (EUR/t), marker area ~ SCH4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>comparison group 10.1002/aenm.201801772 | 400 C | 5 MPa | H2/N2 3 | 6.6e+04 mL/g/h</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>analysis/nh3_field_2026_10_06/candidates.csv</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2262 (group_metrics.csv)</t>
         </is>
@@ -719,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -756,220 +742,412 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>leader changes by paper leaderboard (recycled CO)</t>
+          <t>leader changes by paper leaderboard: inert-limited loop (primary) and STY without the limit</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (primary, variants.leaderboard_*)</t>
+          <t>source: analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv (cost_column) scored with meoh_candidates.aggregate; CI95: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json (STY) and analysis/meoh_main_result_stats_2026_10_06/summary.json (STY_no_limit), cluster_bootstrap.fraction_ci95</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bar height = fraction; hatched height = regret_gt5pct / groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>loop</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>cost_column</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>leaderboard</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>mismatch_groups</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>papers</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STY</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.375</v>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>regret_gt5pct</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>papers_with_mismatch</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>regret_median_mismatched</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>CI95_low</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>CI95_high</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X*S</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" t="n">
+          <t>STY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>STY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inert-limited (primary)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>STY</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>40</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>28</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.375</v>
+      <c r="H5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2237438341570468</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5405405405405406</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8275862068965517</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" t="n">
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>X·S</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>inert-limited (primary)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>40</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>28</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.3</v>
+      <c r="H6" t="n">
+        <v>28</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2237438341570468</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>inert-limited (primary)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3764252722365503</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SMeOH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>S_MeOH</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>31</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>inert-limited (primary)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SMeOH</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>40</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G8" t="n">
         <v>28</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.775</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>marker: STY leaderboard with inert CO</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.inert_opt)</t>
-        </is>
+      <c r="H8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5121683344183094</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STY_no_limit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>STY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>no inlet limit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>STY</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03543670955986696</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t>STY disagreements by kind, inert-limited loop</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inert CO, mismatch groups</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>21</v>
+          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.inlet_limit_6.86pct.kinds)</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>inert CO, fraction</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.525</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>other catalyst</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>comparisons with at least two catalysts</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>error bar on STY: paper-cluster bootstrap</t>
-        </is>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>same catalyst, other temperature</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/summary.json (cluster_bootstrap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>resamples</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CI95 low</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.1515151515151515</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CI95 high</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.5714285714285714</v>
+          <t>comparisons with a temperature series</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1279,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1330,7 +1508,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>x = STY (g_MeOH g_cat-1 h-1), y = cost_recycled_opt (EUR/t), marker area ~ SCH4</t>
+          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCH4; leaders of the inert-limited loop</t>
         </is>
       </c>
     </row>
@@ -1362,27 +1540,52 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
+          <t>SCO</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
           <t>SCH4</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>STY</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>purge_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>cost_recycled_opt</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>purge_recycled_opt</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>STY_leader</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>plant_cost_leader</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>plant_cost_leader_no_limit</t>
         </is>
       </c>
     </row>
@@ -1407,18 +1610,33 @@
         <v>0.97</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.03</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
+        <v>996.8064341210001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="K5" t="n">
         <v>907.428981751</v>
       </c>
-      <c r="I5" t="b">
+      <c r="L5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M5" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="b">
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1443,18 +1661,33 @@
         <v>0.74</v>
       </c>
       <c r="F6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.25</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
+        <v>1765.1390014</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K6" t="n">
         <v>1242.25295316</v>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
+      <c r="L6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1479,18 +1712,33 @@
         <v>0.97</v>
       </c>
       <c r="F7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.01</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.65</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>982.367484386</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K7" t="n">
         <v>896.438398589</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
+      <c r="L7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1515,18 +1763,33 @@
         <v>0.65</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.35</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.65</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>2169.77018622</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K8" t="n">
         <v>1459.37183387</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
+      <c r="L8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1551,18 +1814,33 @@
         <v>0.99</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.55</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
+        <v>921.462422136</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K9" t="n">
         <v>891.802198348</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
+      <c r="L9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1587,18 +1865,33 @@
         <v>0.98</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.02</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
+        <v>982.993781833</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="K10" t="n">
         <v>916.663627744</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
+      <c r="L10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1623,18 +1916,33 @@
         <v>0.46</v>
       </c>
       <c r="F11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.53</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.28</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
+        <v>4160.08196374</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="K11" t="n">
         <v>2096.69366857</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
+      <c r="L11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1659,18 +1967,33 @@
         <v>0.8</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.15</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
+        <v>1862.68974212</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="K12" t="n">
         <v>1234.68078338</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
+      <c r="L12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1695,18 +2018,33 @@
         <v>0.97</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.03</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
+        <v>1087.96098858</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K13" t="n">
         <v>1062.20897971</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
+      <c r="L13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1721,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1758,7 +2096,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>comparison group 10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>comparison group 10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
     </row>
@@ -1772,7 +2110,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>x = STY (g_MeOH g_cat-1 h-1), y = cost_recycled_opt (EUR/t), marker area ~ SCH4</t>
+          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCO; leaders of the inert-limited loop</t>
         </is>
       </c>
     </row>
@@ -1804,423 +2142,256 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
+          <t>SCO</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
           <t>SCH4</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>STY</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>cost_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>purge_recycled_opt_inlet</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>cost_recycled_opt</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>purge_recycled_opt</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>STY_leader</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>plant_cost_leader</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>plant_cost_leader_no_limit</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fig 8, Cu-Ba/Al2O3, 473 K, 10 MPa</t>
+          <t>Fig. 2B, InNi3C0.5/m-ZrO2, 24000 ml gcat-1 hour-1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cu–Ba/Al2O3 [Fig 8, Cu-Ba/Al2O3, 473 K, 10 MPa]</t>
+          <t>InNi3C0.5/m-ZrO2 [Fig. 2B, InNi3C0.5/m-ZrO2, 24000 ml gcat-1 hour-1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>199.85</v>
+        <v>300</v>
       </c>
       <c r="D5" t="n">
-        <v>0.028</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.622</v>
+        <v>0.879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0519</v>
+        <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>1170.17134434</v>
-      </c>
-      <c r="I5" t="b">
+        <v>0.62</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1288.91445101</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K5" t="n">
+        <v>918.752365764</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M5" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fig 5/Fig 6, Cu/Al2O3, 503 K, 10 MPa</t>
+          <t>Fig. 2B, InNi3C0.5/t-ZrO2, 24000 ml gcat-1 hour-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cu/Al2O3 [Fig 5/Fig 6, Cu/Al2O3, 503 K, 10 MPa]</t>
+          <t>InNi3C0.5/t-ZrO2 [Fig. 2B, InNi3C0.5/t-ZrO2, 24000 ml gcat-1 hour-1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>229.85</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>0.121</v>
+        <v>0.039</v>
       </c>
       <c r="E6" t="n">
-        <v>0.119</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.115</v>
+        <v>0.098</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0435</v>
+        <v>0.002</v>
       </c>
       <c r="H6" t="n">
-        <v>1081.52892928</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
+        <v>0.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1258.44545047</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1026.40267116</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fig 5/Fig 6, Cu/Al2O3, 473 K, 10 MPa</t>
+          <t>Fig. 2B, InNi3C0.5/a-ZrO2, 24000 ml gcat-1 hour-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cu/Al2O3 [Fig 5/Fig 6, Cu/Al2O3, 473 K, 10 MPa]</t>
+          <t>InNi3C0.5/a-ZrO2 [Fig. 2B, InNi3C0.5/a-ZrO2, 24000 ml gcat-1 hour-1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>199.85</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.466</v>
+        <v>0.892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.081</v>
+        <v>0.106</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0337</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>1363.00923765</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
+        <v>0.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1328.55200442</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1102.72415785</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fig 5/Fig 6, Cu/Al2O3, 533 K, 10 MPa</t>
+          <t>Fig. 2B, InNi3C0.5/SiO2, 24000 ml gcat-1 hour-1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cu/Al2O3 [Fig 5/Fig 6, Cu/Al2O3, 533 K, 10 MPa]</t>
+          <t>InNi3C0.5/SiO2 [Fig. 2B, InNi3C0.5/SiO2, 24000 ml gcat-1 hour-1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>259.85</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>0.163</v>
+        <v>0.022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.045</v>
+        <v>0.949</v>
       </c>
       <c r="F8" t="n">
-        <v>0.103</v>
+        <v>0.05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0222</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>1067.49027074</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fig 5/Fig 6, Cu/Al2O3, 553 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cu/Al2O3 [Fig 5/Fig 6, Cu/Al2O3, 553 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>279.85</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0201</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1104.6727405</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fig 5/Fig 6, Cu/Al2O3, 443 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cu/Al2O3 [Fig 5/Fig 6, Cu/Al2O3, 443 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>169.85</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1882.44652844</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fig 7, Cu-K/Al2O3, 503 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cu–K/Al2O3 [Fig 7, Cu-K/Al2O3, 503 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>229.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0063</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1054.67603102</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fig 7, Cu-K/Al2O3, 553 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Cu–K/Al2O3 [Fig 7, Cu-K/Al2O3, 553 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>279.85</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1002.0514943</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
+        <v>0.18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1137.52273359</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1101.28449922</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fig 7/Fig 8, Cu-K/Al2O3, 473 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Cu–K/Al2O3 [Fig 7/Fig 8, Cu-K/Al2O3, 473 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>199.85</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1183.21956718</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fig 7, Cu-K/Al2O3, 533 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Cu–K/Al2O3 [Fig 7, Cu-K/Al2O3, 533 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>259.85</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1035.48720019</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fig 7, Cu-K/Al2O3, 443 K, 10 MPa</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cu–K/Al2O3 [Fig 7, Cu-K/Al2O3, 443 K, 10 MPa]</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>169.85</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1489.71735261</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -539,10 +539,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/summary.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bar height = fraction; hatched height = regret_gt5pct_groups / groups (primary only)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -557,7 +561,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/summary.json (primary.mismatch_kinds); plant-winner metal from group_metrics.csv + candidates.csv</t>
+          <t>analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -619,12 +623,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/candidates.csv</t>
+          <t>analysis/nh3_field_2026_10_06/nh3_1_2/candidates_printed.csv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2262 (group_metrics.csv)</t>
+          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.1376 (group_metrics_printed.csv)</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1205,245 +1209,260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_field_2026_10_06/summary.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers)</t>
+          <t>source: analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bar height = fraction; hatched height = regret_gt5pct_groups / groups (primary only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>leaderboard</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>mismatch_groups</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>groups</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>papers</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>CI95_low</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>CI95_high</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>rate per g catalyst (primary)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>44</v>
-      </c>
-      <c r="C4" t="n">
-        <v>124</v>
-      </c>
-      <c r="D4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3548387096774194</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1843924972004479</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5241492368569812</v>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>regret_gt5pct_groups</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rate per g metal</t>
+          <t>rate per g catalyst (primary)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2814814814814815</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5947779938421649</v>
+        <v>0.375</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>rate per g metal</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>rate per g catalyst, 90 % Ru recovery</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>43</v>
-      </c>
-      <c r="C6" t="n">
-        <v>124</v>
-      </c>
-      <c r="D6" t="n">
-        <v>28</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.3467741935483871</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5109571373689697</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2758620689655172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>what the mismatched comparisons differ by (primary)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>source: analysis/nh3_field_2026_10_06/summary.json (primary.mismatch_kinds); plant-winner metal from group_metrics.csv + candidates.csv</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>source: analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>mechanism</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>groups</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>papers</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>regret_median</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>regret_max</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>of_which_plant_winner_is_Fe</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>different metal</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.1712728367906377</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6211888921974211</v>
-      </c>
-      <c r="F12" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fused-Fe reference vs supported catalyst</t>
+          <t>different metal</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2873732745288964</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3726866579010616</v>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2866219126896772</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7648114725882532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>same metal and metal content</t>
+          <t>fused-Fe reference vs supported catalyst</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0225796197425291</v>
+        <v>0.1177606285481737</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0591389851267043</v>
+        <v>0.2205124766725894</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>same metal and metal content</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0243868701812627</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0243868701812627</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>same metal, different metal content</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.004949565365879021</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.00960141583510787</v>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01100387998080251</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.01100387998080251</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2450,14 +2469,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_field_2026_10_06/candidates.csv</t>
+          <t>source: analysis/nh3_field_2026_10_06/nh3_1_2/candidates_printed.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.2262 (group_metrics.csv)</t>
+          <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.1376 (group_metrics_printed.csv)</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2540,7 @@
         <v>2740</v>
       </c>
       <c r="E5" t="n">
-        <v>25.7689</v>
+        <v>20.8908</v>
       </c>
       <c r="F5" t="n">
         <v>2.74</v>
@@ -2551,7 +2570,7 @@
         <v>4100</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9995</v>
+        <v>20.1208</v>
       </c>
       <c r="F6" t="n">
         <v>4.1</v>
@@ -2566,7 +2585,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ru/BaTiO2.65H0.35</t>
+          <t>Ru/BaTiO2.5H0.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2575,16 +2594,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="D7" t="n">
-        <v>13000</v>
+        <v>28200</v>
       </c>
       <c r="E7" t="n">
-        <v>23.509</v>
+        <v>17.586</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>28.2</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -2605,19 +2624,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.86</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>28200</v>
+        <v>50000</v>
       </c>
       <c r="E8" t="n">
-        <v>22.9751</v>
+        <v>16.9806</v>
       </c>
       <c r="F8" t="n">
-        <v>28.2</v>
+        <v>50</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -2626,28 +2645,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ru/BaTiO2.5H0.5</t>
+          <t>Co/BaTiO2.37H0.63</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>50000</v>
+        <v>5500</v>
       </c>
       <c r="E9" t="n">
-        <v>24.4496</v>
+        <v>23.0408</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>5.5</v>
       </c>
       <c r="G9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -2656,25 +2675,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ru/BaTiO2.5N0.3◻0.2</t>
+          <t>Fe/BaTiO3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="E10" t="n">
-        <v>26.5156</v>
+        <v>29.9411</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -2686,55 +2705,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Co/BaTiO2.37H0.63</t>
+          <t>Fe/BaTiO2.35H0.65</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5500</v>
+        <v>14000</v>
       </c>
       <c r="E11" t="n">
-        <v>33.8399</v>
+        <v>14.9261</v>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fe/BaTiO3</t>
+          <t>Ru/CaTiO2.77H0.23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>5370</v>
       </c>
       <c r="E12" t="n">
-        <v>36.1553</v>
+        <v>19.5858</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2</v>
+        <v>5.37</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -2746,37 +2765,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fe/BaTiO2.35H0.65</t>
+          <t>Ru/SrTiO2.59H0.41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="E13" t="n">
-        <v>19.9395</v>
+        <v>18.3951</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ru/CaTiO2.77H0.23</t>
+          <t>Ru/BaTiO2.67H0.33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2785,16 +2804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5370</v>
+        <v>30500</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7523</v>
+        <v>17.4918</v>
       </c>
       <c r="F14" t="n">
-        <v>5.37</v>
+        <v>30.5</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -2806,7 +2825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ru/SrTiO2.59H0.41</t>
+          <t>Ru/CaTiO3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2815,16 +2834,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="D15" t="n">
-        <v>15000</v>
+        <v>770</v>
       </c>
       <c r="E15" t="n">
-        <v>23.3775</v>
+        <v>24.3884</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>0.77</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -2836,7 +2855,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ru/BaTiO2.67H0.33</t>
+          <t>Ru/SrTiO3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2845,16 +2864,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="D16" t="n">
-        <v>30500</v>
+        <v>2030</v>
       </c>
       <c r="E16" t="n">
-        <v>22.8086</v>
+        <v>21.2961</v>
       </c>
       <c r="F16" t="n">
-        <v>30.5</v>
+        <v>2.03</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -2866,120 +2885,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ru/CaTiO3</t>
+          <t>Co/BaTiO2.4H0.6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>770</v>
+        <v>4000</v>
       </c>
       <c r="E17" t="n">
-        <v>29.7915</v>
+        <v>26.2542</v>
       </c>
       <c r="F17" t="n">
-        <v>0.77</v>
+        <v>4</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ru/SrTiO3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ru</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2030</v>
-      </c>
-      <c r="E18" t="n">
-        <v>26.5665</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ru/BaTiO3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ru</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>26.4051</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Co/BaTiO2.4H0.6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E20" t="n">
-        <v>43.202</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
         <v>0</v>
       </c>
     </row>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv (cost_column) scored with meoh_candidates.aggregate; CI95: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json (STY) and analysis/meoh_main_result_stats_2026_10_06/summary.json (STY_no_limit), cluster_bootstrap.fraction_ci95</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/pooled_candidates.csv (both extractions; cost_column) scored with meoh_candidates.aggregate; CI95: analysis/meoh_field_pooled_2026_10_15/summary.json (S6 / S5 primary.bootstrap_frozen_inversion.ci95)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.inlet_limit_6.86pct.kinds)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6.kinds)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv (cost_column) scored with meoh_candidates.aggregate; CI95: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json (STY) and analysis/meoh_main_result_stats_2026_10_06/summary.json (STY_no_limit), cluster_bootstrap.fraction_ci95</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/pooled_candidates.csv (both extractions; cost_column) scored with meoh_candidates.aggregate; CI95: analysis/meoh_field_pooled_2026_10_15/summary.json (S6 / S5 primary.bootstrap_frozen_inversion.ci95)</t>
         </is>
       </c>
     </row>
@@ -863,31 +863,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2237438341570468</v>
+        <v>0.3703543069492815</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.4888690476190476</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -917,25 +917,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2237438341570468</v>
+        <v>0.3885738456859771</v>
       </c>
     </row>
     <row r="7">
@@ -965,25 +965,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="I7" t="n">
-        <v>0.675</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3764252722365503</v>
+        <v>0.6139646532492606</v>
       </c>
     </row>
     <row r="8">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>0.425</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5121683344183094</v>
+        <v>0.3376083189067868</v>
       </c>
     </row>
     <row r="9">
@@ -1061,31 +1061,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.308641975308642</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
         <v>15</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03543670955986696</v>
+        <v>0.03543670951859796</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1690095116151454</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4459623458409864</v>
       </c>
     </row>
     <row r="12">
@@ -1098,7 +1098,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.inlet_limit_6.86pct.kinds)</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/summary.json (S6.kinds)</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
+          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
+          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_2026_10_06/nh3_1_2/candidates_printed.csv</t>
+          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/candidates_printed.csv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
+          <t>source: analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
         </is>
       </c>
     </row>
@@ -1269,25 +1269,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.375</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1297,22 +1297,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1142857142857143</v>
+        <v>0.1956389183457052</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4888888888888889</v>
       </c>
     </row>
     <row r="7">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2758620689655172</v>
+        <v>0.3571428571428572</v>
       </c>
     </row>
     <row r="10">
@@ -1350,7 +1350,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_field_2026_10_06/nh3_1_2/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
+          <t>source: analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
         </is>
       </c>
     </row>
@@ -1415,16 +1415,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1177606285481737</v>
+        <v>0.2205124766725894</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2205124766725894</v>
+        <v>0.2826473793073277</v>
       </c>
     </row>
     <row r="15">
@@ -1434,16 +1434,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0243868701812627</v>
+        <v>0.03916387043013219</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0243868701812627</v>
+        <v>0.05394087067900168</v>
       </c>
     </row>
     <row r="16">
@@ -1453,16 +1453,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01100387998080251</v>
+        <v>0.01729198120132055</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01100387998080251</v>
+        <v>0.02358008242183859</v>
       </c>
     </row>
   </sheetData>
@@ -2469,7 +2469,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_field_2026_10_06/nh3_1_2/candidates_printed.csv</t>
+          <t>source: analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/candidates_printed.csv</t>
         </is>
       </c>
     </row>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -516,12 +516,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>STY disagreements by kind, inert-limited loop</t>
+          <t>STY leader changes catalyst against catalyst (each catalyst at its best measured point), inert-limited loop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6.kinds)</t>
+          <t>analysis/meoh_catalyst_level_2026_10_19/summary.json (cat_primary.comparison)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1091,14 +1091,14 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>STY disagreements by kind, inert-limited loop</t>
+          <t>STY leader changes catalyst against catalyst (each catalyst at its best measured point), inert-limited loop</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_field_pooled_2026_10_15/summary.json (S6.kinds)</t>
+          <t>source: analysis/meoh_catalyst_level_2026_10_19/summary.json (cat_primary.comparison)</t>
         </is>
       </c>
     </row>
@@ -1117,41 +1117,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>other catalyst</t>
+          <t>comparisons with at least two catalysts</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>comparisons with at least two catalysts</t>
+          <t>leader is another catalyst</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>same catalyst, other temperature</t>
+          <t>of which cost gap above 5 %</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>comparisons with a temperature series</t>
+          <t>CI95 low (paper bootstrap)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43</v>
+        <v>0.2941176470588235</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CI95 high (paper bootstrap)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5333561643835613</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_Fig2.xlsx
+++ b/source_data/SourceData_Fig2.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -524,27 +524,31 @@
           <t>analysis/meoh_catalyst_level_2026_10_19/summary.json (cat_primary.comparison)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>second bar (cat., lab. X)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ammonia leader changes</t>
+          <t>STY leader changes catalyst against catalyst, each entry free to raise its conversion to 0.95 X_eq with catalyst amount (primary count), inert-limited loop</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
+          <t>analysis/meoh_catalyst_level_2026_10_19/summary.json (conversion_raised.cost_f0.95.cat_primary); per group: groups_catalyst_level_conversion_raised.csv</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bar height = fraction; hatched height = regret_gt5pct_groups / groups (primary only)</t>
+          <t>first bar (cat., X raised)</t>
         </is>
       </c>
     </row>
@@ -556,47 +560,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>what the mismatched comparisons differ by (primary)</t>
+          <t>ammonia leader changes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary, variants.per_g_metal_leaderboard, variants.Ru_recovery_90pct; bootstrap_papers, regret_bins)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bar height = fraction; hatched height = regret_gt5pct_groups / groups (primary only)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comparison group 10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+          <t>what the mismatched comparisons differ by (primary)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCH4; leaders of the inert-limited loop</t>
-        </is>
-      </c>
+          <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/summary_printed.json (primary.mismatch_kinds); plant-winner metal from group_metrics_printed.csv (plant_winner_metal)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comparison group 10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>comparison group 10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -606,27 +610,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCO; leaders of the inert-limited loop</t>
+          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCH4; leaders of the inert-limited loop</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>comparison group 10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>analysis/meoh_literature_inversion_2026_10_05/literature_candidates.csv</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>x = STY (g_MeOH g_cat-1 h-1); filled y = cost_recycled_opt_inlet (EUR/t, inert-limited loop; purge_recycled_opt_inlet, fraction of loop gas); open y = cost_recycled_opt (no limit); marker area ~ SCO; leaders of the inert-limited loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>f</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>comparison group 10.1002/aenm.201801772 | 400 C | 5 MPa | H2/N2 3 | 6.6e+04 mL/g/h</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>analysis/nh3_field_expansion_2026_10_12/nh3_1_2/runs/pooled_vf_screen/candidates_printed.csv</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>paper_rate in umol g_cat-1 h-1; regret of the rate leader 0.1376 (group_metrics_printed.csv)</t>
         </is>
@@ -709,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -893,12 +919,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>X·S</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -913,7 +939,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -923,30 +949,30 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6172839506172839</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3885738456859771</v>
+        <v>0.6139646532492606</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>SMeOH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>S_MeOH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -961,7 +987,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>SMeOH</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -971,45 +997,45 @@
         <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="J7" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6139646532492606</v>
+        <v>0.3376083189067868</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SMeOH</t>
+          <t>STY_no_limit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S_MeOH</t>
+          <t>STY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>inert-limited (primary)</t>
+          <t>no inlet limit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cost_recycled_opt_inlet</t>
+          <t>cost_recycled_opt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SMeOH</t>
+          <t>STY</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1019,86 +1045,45 @@
         <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.308641975308642</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3376083189067868</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STY_no_limit</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>STY</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>no inlet limit</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>cost_recycled_opt</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>STY</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>81</v>
-      </c>
-      <c r="G9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H9" t="n">
-        <v>25</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.308641975308642</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15</v>
-      </c>
-      <c r="L9" t="n">
         <v>0.03543670951859796</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M8" t="n">
         <v>0.1690095116151454</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N8" t="n">
         <v>0.4459623458409864</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>STY leader changes catalyst against catalyst (each catalyst at its best measured point), inert-limited loop</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>STY leader changes catalyst against catalyst (each catalyst at its best measured point), inert-limited loop</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_catalyst_level_2026_10_19/summary.json (cat_primary.comparison)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_catalyst_level_2026_10_19/summary.json (cat_primary.comparison)</t>
+          <t>second bar (cat., lab. X)</t>
         </is>
       </c>
     </row>
@@ -1162,6 +1147,99 @@
       </c>
       <c r="B19" t="n">
         <v>0.5333561643835613</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>STY leader changes catalyst against catalyst, each entry free to raise its conversion to 0.95 X_eq with catalyst amount (primary count), inert-limited loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_catalyst_level_2026_10_19/summary.json (conversion_raised.cost_f0.95.cat_primary); per group: groups_catalyst_level_conversion_raised.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>first bar (cat., X raised)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>comparisons with at least two catalysts</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>leader is another catalyst</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>of which cost gap above 5 %</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CI95 low (paper bootstrap)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.2205820039880359</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CI95 high (paper bootstrap)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.459016393442623</v>
       </c>
     </row>
   </sheetData>
